--- a/output/reporte_h2_RM_2026.xlsx
+++ b/output/reporte_h2_RM_2026.xlsx
@@ -13,10 +13,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Establecimiento" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Region'!$A$1:$D$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SS'!$A$1:$E$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comuna'!$A$1:$F$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Establecimiento'!$A$1:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Region'!$A$1:$D$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SS'!$A$1:$E$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comuna'!$A$1:$F$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Establecimiento'!$A$1:$G$124</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -490,21 +490,261 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1013</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1712</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0.5917056074766355</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Arica Parinacota</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>755</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>785</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>0.9617834394904459</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>725</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>811</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>0.8939580764488286</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Aysén del General Carlos Ibañez del Campo</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>326</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.6073619631901841</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>2705</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>3033</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0.891856247939334</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1956</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>2120</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0.9226415094339623</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>2077</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>2761</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0.7522636725823977</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>1813</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>2124</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0.853578154425612</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>2090</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>2294</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0.9110723626852659</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>571</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>767</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0.7444589308996089</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Magallanes y de la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>375</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>379</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0.9894459102902374</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>Maule</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>1758</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>1952</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>0.9006147540983607</v>
+      <c r="B13" s="3" t="n">
+        <v>2910</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>3249</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0.8956602031394275</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>12173</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>13915</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>0.8748113546532519</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>908</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>1335</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0.6801498127340824</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>3327</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>3808</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0.873686974789916</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>838</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>952</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0.8802521008403361</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D2"/>
+  <autoFilter ref="A1:D17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -515,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -555,26 +795,635 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Antofagasta</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1013</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>1712</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.5917056074766355</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Arica Parinacota</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>755</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>785</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.9617834394904459</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Atacama</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>725</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>811</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0.8939580764488286</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Aysén del General Carlos Ibañez del Campo</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aysén</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>326</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0.6073619631901841</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Arauco</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>293</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>376</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0.7792553191489362</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>870</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>928</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Concepción</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>922</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1059</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0.8706326723323891</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Talcahuano</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>620</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>670</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0.9253731343283582</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1956</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>2120</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>0.9226415094339623</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Norte</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>205</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>610</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>0.3360655737704918</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1872</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>2151</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0.8702928870292888</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>1813</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>2124</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0.853578154425612</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Chiloé</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>424</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>507</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>0.8362919132149902</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Reloncaví</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1195</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0.9623430962343096</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Osorno</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>516</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>592</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0.8716216216216216</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>571</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>767</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0.7444589308996089</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Magallanes y de la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Magallanes</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>375</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>379</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>0.9894459102902374</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
           <t>Maule</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>1758</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>1952</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>0.9006147540983607</v>
+      <c r="C19" s="3" t="n">
+        <v>2910</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>3249</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0.8956602031394275</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Central</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>2033</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2195</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>0.9261958997722096</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Norte</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>1650</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1885</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>0.8753315649867374</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>2505</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>3018</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>0.8300198807157058</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Oriente</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>1136</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1224</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>0.9281045751633987</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>2320</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>2614</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>0.8875286916602907</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>2529</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>2979</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>0.8489425981873112</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Tarapacá</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>908</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1335</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>0.6801498127340824</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aconcagua</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>756</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>801</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>0.9438202247191011</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Oriente</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>1.114285714285714</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Valparaíso San Antonio</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1032</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1116</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>0.9247311827956989</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1856</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>0.8081896551724138</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>838</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>952</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>0.8802521008403361</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E2"/>
+  <autoFilter ref="A1:E31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -585,7 +1434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -631,213 +1480,3173 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>22</v>
+        <v>465</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>25</v>
+        <v>994</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.88</v>
+        <v>0.4678068410462777</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Constitución</t>
+          <t>Calama</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6</v>
+        <v>529</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>11</v>
+        <v>693</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.7633477633477633</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Curicó</t>
+          <t>Mejillones</t>
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>507</v>
+        <v>2</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>529</v>
+        <v>3</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.9584120982986768</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Licantén</t>
+          <t>Taltal</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Linares</t>
+          <t>Tocopilla</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>287</v>
+        <v>12</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>357</v>
+        <v>17</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.803921568627451</v>
+        <v>0.7058823529411765</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica Parinacota</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Arica y Parinacota</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Parral</t>
+          <t>Arica</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>9</v>
+        <v>755</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>20</v>
+        <v>785</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.45</v>
+        <v>0.9617834394904459</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Atacama</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>San Javier</t>
+          <t>Chañaral</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.6956521739130435</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Atacama</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>494</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>575</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0.8591304347826086</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Atacama</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>229</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>235</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0.9744680851063829</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Aysén del General Carlos Ibañez del Campo</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aysén</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Aisén</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Aysén del General Carlos Ibañez del Campo</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aysén</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Aysén del General Carlos Ibañez del Campo</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aysén</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Cochrane</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Aysén del General Carlos Ibañez del Campo</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aysén</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>184</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>308</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>0.5974025974025974</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Arauco</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Cañete</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Arauco</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Curanilahue</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>263</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>342</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>0.7690058479532164</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Arauco</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Lebu</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Laja</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Los Ángeles</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>919</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0.9423286180631121</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Mulchén</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Santa Bárbara</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Concepción</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>801</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0.8863920099875156</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Concepción</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Coronel</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>223</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>0.8116591928251121</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Concepción</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Lota</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Talcahuano</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Penco</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Talcahuano</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Talcahuano</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>613</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>661</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0.9273827534039334</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Talcahuano</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Tome</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>786</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>827</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>0.9504232164449818</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>579</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>611</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>0.9476268412438625</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>440</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>489</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>0.8997955010224948</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Norte</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Angol</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>332</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>0.3343373493975904</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Norte</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Norte</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Norte</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Norte</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>272</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0.3419117647058824</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>0.5737704918032787</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>0.9836065573770492</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>1335</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>1558</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>0.8568677792041078</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>373</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>397</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>0.9395465994962217</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Graneros</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Lolol</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Nancagua</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Peumo</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Pichidegua</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Pichilemu</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Rancagua</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>836</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>1018</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>0.8212180746561886</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Rengo</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>336</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>401</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>0.8379052369077307</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>San Fernando</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>315</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>349</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>0.9025787965616046</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>San Vicente</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>0.8518518518518519</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>298</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>314</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>0.9490445859872612</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Chiloé</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Chiloé</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>315</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Chiloé</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>0.8045977011494253</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Reloncaví</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Reloncaví</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Reloncaví</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>1147</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>1192</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>0.962248322147651</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Osorno</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>516</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>592</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>0.8716216216216216</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Río Bueno</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>516</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>697</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>0.7403156384505022</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Magallanes y de la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Magallanes</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>0.958904109589041</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Magallanes y de la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Magallanes</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>305</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>306</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>0.9967320261437909</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
           <t>Maule</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>0.8809523809523809</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>847</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>877</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>0.9657924743443558</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>476</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>588</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>0.5319148936170213</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>San Javier</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Talca</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
-        <v>911</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>986</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>0.9239350912778904</v>
+      <c r="D88" s="3" t="n">
+        <v>1492</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>1642</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>0.9086479902557856</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Central</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>925</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>955</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>0.9685863874345549</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Central</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>1108</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>1240</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>0.8935483870967742</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Norte</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Norte</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>1650</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>1881</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>0.8771929824561403</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>951</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>1090</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>0.8724770642201835</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>472</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>571</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>0.8266199649737302</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Peñaflor</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>910</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>931</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>0.9774436090225563</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>402</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>0.3855721393034826</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Oriente</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="n">
+        <v>1136</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>1224</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>0.9281045751633987</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>281</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>306</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>0.9183006535947712</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>1226</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>1289</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>0.9511249030256013</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>813</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>1019</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>0.7978410206084396</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>898</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>0.8351893095768375</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>1025</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>1264</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>0.8109177215189873</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>754</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>817</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>0.9228886168910648</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Tarapacá</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Tarapacá</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>890</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>1316</v>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>0.6762917933130699</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aconcagua</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Llaillay</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aconcagua</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Los Andes</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>276</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>0.9601449275362319</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aconcagua</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>San Felipe</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>491</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>523</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>0.9388145315487572</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Oriente</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Isla de Pascua</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>1.114285714285714</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Valparaíso San Antonio</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>458</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>483</v>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>0.94824016563147</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Valparaíso San Antonio</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>574</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>633</v>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>0.9067930489731437</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Cabildo</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F113" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Calera</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>La Ligua</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Limache</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Quillota</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>521</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>579</v>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>0.8998272884283247</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Quilpué</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>417</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>0.4700239808153477</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Viña del Mar</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>779</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>0.9164705882352941</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>643</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>754</v>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>0.8527851458885941</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>187</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>0.9842105263157894</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F9"/>
+  <autoFilter ref="A1:F123"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -848,7 +4657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -900,253 +4709,3814 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios (Cauquenes)</t>
+          <t>Hospital Dr. Leonardo Guzmán (Antofagasta)</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>22</v>
+        <v>465</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>25</v>
+        <v>994</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.88</v>
+        <v>0.4678068410462777</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Constitución</t>
+          <t>Calama</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Constitución</t>
+          <t>Hospital Dr. Carlos Cisternas (Calama)</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>6</v>
+        <v>529</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>11</v>
+        <v>693</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.7633477633477633</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Curicó</t>
+          <t>Mejillones</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios (Curicó)</t>
+          <t>Hospital de Mejillones</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>507</v>
+        <v>2</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>529</v>
+        <v>3</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.9584120982986768</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Licantén</t>
+          <t>Taltal</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Licantén</t>
+          <t>Hospital 21 de Mayo (Taltal)</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>1</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Linares</t>
+          <t>Tocopilla</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Hospital Presidente Carlos Ibáñez del Campo (Linares)</t>
+          <t>Hospital Dr. Marcos Macuada (Tocopilla)</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>287</v>
+        <v>12</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>357</v>
+        <v>17</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.803921568627451</v>
+        <v>0.7058823529411765</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica Parinacota</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Arica y Parinacota</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Parral</t>
+          <t>Arica</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Hospital San José (Parral)</t>
+          <t>Hospital Regional Dr. Juan Noé Crevani (Arica)</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>9</v>
+        <v>755</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>20</v>
+        <v>785</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.45</v>
+        <v>0.9617834394904459</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Atacama</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>San Javier</t>
+          <t>Chañaral</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Abel Fuentealba Lagos de San Javier</t>
+          <t>Hospital Dr. Jerónimo Méndez Arancibia (Chañaral)</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.6956521739130435</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Atacama</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San José del Carmen (Copiapó)</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>494</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>575</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0.8591304347826086</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Atacama</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Provincial del Huasco Monseñor Fernando Ariztía Ruiz (Vallenar)</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>229</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>235</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>0.9744680851063829</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Aysén del General Carlos Ibañez del Campo</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aysén</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Aisén</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Puerto Aysén</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Aysén del General Carlos Ibañez del Campo</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aysén</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Chile Chico</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Leopoldo Ortega Rodríguez (Chile Chico)</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Aysén del General Carlos Ibañez del Campo</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aysén</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Cochrane</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Lord Cochrane</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Aysén del General Carlos Ibañez del Campo</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aysén</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Coyhaique</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Regional de Coyhaique</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>184</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>308</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0.5974025974025974</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Arauco</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Cañete</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Intercultural Kallvu Llanka (Cañete)</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>29</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0.9354838709677419</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Arauco</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Curanilahue</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Provincial Dr. Rafael Avaría (Curanilahue)</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>263</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>342</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0.7690058479532164</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Arauco</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Lebu</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Lebu</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Laja</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Comunitario de Laja</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Los Ángeles</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Complejo Asistencial Dr. Víctor Ríos Ruiz (Los Ángeles)</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>919</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0.9423286180631121</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Mulchén</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Mulchén</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Biobío</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Santa Bárbara</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Comunitario de Santa Bárbara</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Concepción</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Concepción</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Clínico Regional Dr. Guillermo Grant Benavente (Concepción)</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>710</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>801</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>0.8863920099875156</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Concepción</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Coronel</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San José (Coronel)</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>181</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>223</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0.8116591928251121</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Concepción</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Lota</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Lota</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Talcahuano</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Penco</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Penco Lirquén</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Talcahuano</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Talcahuano</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Las Higueras (Talcahuano)</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>613</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>661</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0.9273827534039334</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Talcahuano</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Tome</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Tomé</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Pablo (Coquimbo)</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>786</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>827</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>0.9504232164449818</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Humberto Elorza Cortés (Illapel)</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>168</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Juan de Dios (La Serena)</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>579</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>611</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>0.9476268412438625</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Pedro (Los Vilos)</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Antonio Tirado Lanas de Ovalle</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>440</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>489</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>0.8997955010224948</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Salamanca</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Coquimbo</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Juan de Dios (Vicuña)</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Norte</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Angol</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Mauricio Heyermann (Angol)</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>332</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>0.3343373493975904</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Norte</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Collipulli</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Collipulli</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Norte</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Lonquimay</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Lonquimay</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Norte</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Traiguén</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Dino Stagno M.(Traiguén)</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Norte</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San José de Victoria</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>272</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>0.3419117647058824</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Carahue</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Familiar y Comunitario Carahue</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Cunco</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Eduardo González Galeno (Cunco)</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Galvarino</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Galvarino</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Gorbea</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Gorbea</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Lautaro</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Abraham Godoy Peña (Lautaro)</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>0.5737704918032787</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Loncoche</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Familiar y Comunitario de Loncoche</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Intercultural de Nueva Imperial</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>0.9836065573770492</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Pitrufquén</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Pitrufquén</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Pucón</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Francisco de Pucón (D)</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Saavedra</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Arturo Hillerns Larrañaga (Saavedra)</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Hernán Henríquez Aravena (Temuco)</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>1335</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>1558</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>0.8568677792041078</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Toltén</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Toltén</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>La Araucanía</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Araucanía Sur</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Villarrica</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Villarrica</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>373</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>397</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>0.9395465994962217</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Graneros</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Santa Filomena de Graneros</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Lolol</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Lolol</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Nancagua</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Nancagua</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Peumo</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Del Salvador de Peumo</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Pichidegua</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Pichidegua</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Pichilemu</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Pichilemu</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Rancagua</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Franco Ravera Zunino</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>836</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>1018</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>0.8212180746561886</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Rengo</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Ricardo Valenzuela Sáez (Rengo)</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>336</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>401</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>0.8379052369077307</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>San Fernando</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Juan de Dios de San Fernando</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>315</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>349</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>0.9025787965616046</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>San Vicente</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Vicente de Tagua -Tagua</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>0.8518518518518519</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Libertador Gral. B. O'Higgins</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Santa Cruz</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Santa Cruz</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>298</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>314</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>0.9490445859872612</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Chiloé</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Ancud</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Ancud</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Chiloé</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Castro</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Castro</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>270</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>315</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Chiloé</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Quellón</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Quellón</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>0.8045977011494253</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Reloncaví</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Calbuco</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Calbuco</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Reloncaví</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Frutillar</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Reloncaví</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Puerto Montt</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Puerto Montt</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>1147</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>1192</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>0.962248322147651</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Osorno</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Osorno</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Base San José de Osorno</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>516</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>592</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>0.8716216216216216</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Juan Morey (La Unión)</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Lanco</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Los Lagos</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Santa Elisa de San José de la Mariquina</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Paillaco</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Panguipulli</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Río Bueno</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Río Bueno</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Los Rios</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Base Valdivia</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>516</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>697</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>0.7403156384505022</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Magallanes y de la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Magallanes</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Augusto Essmann Burgos ( Natales)</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>0.958904109589041</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Magallanes y de la Antártica Chilena</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Magallanes</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Clínico de Magallanes Dr. Lautaro Navarro Avaria</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>305</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>306</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>0.9967320261437909</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
           <t>Maule</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Juan de Dios (Cauquenes)</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>0.8809523809523809</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Constitución</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Juan de Dios (Curicó)</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>847</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>877</v>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>0.9657924743443558</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Licantén</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Presidente Carlos Ibáñez del Campo (Linares)</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>476</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>588</v>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San José (Parral)</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>0.5319148936170213</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>San Javier</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Abel Fuentealba Lagos de San Javier</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Del Maule</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Talca</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Hospital Dr. César Garavagno Burotto (Talca)</t>
         </is>
       </c>
-      <c r="E9" s="3" t="n">
-        <v>911</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>986</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>0.9239350912778904</v>
+      <c r="E88" s="3" t="n">
+        <v>1492</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>1642</v>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>0.9086479902557856</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Central</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Maipú</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Clínico Metropolitano El Carmen Doctor Luis Valentín Ferrada</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>925</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>955</v>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>0.9685863874345549</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Central</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Clínico San Borja Arriarán</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>1240</v>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>0.8935483870967742</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Norte</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Colina</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>SAR Colina</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Norte</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Complejo Hospitalario San José (Santiago, Independencia)</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>1881</v>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>0.8771929824561403</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Cerro Navia</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Hospital  Félix Bulnes Cerda</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>951</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>1090</v>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>0.8724770642201835</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San José (Melipilla)</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>472</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>571</v>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>0.8266199649737302</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Peñaflor</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Peñaflor</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Juan de Dios (Santiago, Santiago)</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>910</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>931</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>0.9774436090225563</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Occidente</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Talagante</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Adalberto Steeger (Talagante)</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>402</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>0.3855721393034826</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Oriente</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Peñalolén</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Luis Tisné B. (Santiago, Peñalolén)</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>1136</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>1224</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0.9281045751633987</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Luis (Buin)</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>281</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>306</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>0.9183006535947712</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Hospital El Pino (Santiago, San Bernardo)</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>779</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>812</v>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>0.9593596059113301</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>San Bernardo</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Parroquial de San Bernardo (D)</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>447</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>477</v>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>0.9371069182389937</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>San Miguel</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Barros Luco Trudeau (Santiago, San Miguel)</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>813</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>1019</v>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>0.7978410206084396</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>La Florida</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Clínico Metropolitano La Florida Dra. Eloísa Díaz Insunza</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>898</v>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>0.8351893095768375</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Complejo Hospitalario Dr. Sótero del Río (Santiago, Puente Alto)</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>1025</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>1264</v>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>0.8109177215189873</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Padre Alberto Hurtado (San Ramón)</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>754</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>817</v>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>0.9228886168910648</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Tarapacá</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Tarapacá</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Ernesto Torres Galdames (Iquique)</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>890</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>1316</v>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>0.6762917933130699</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aconcagua</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Llaillay</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Francisco (Llaillay)</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aconcagua</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Los Andes</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Juan de Dios (Los Andes)</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>276</v>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>0.9601449275362319</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Aconcagua</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>San Felipe</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Camilo de San Felipe</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>491</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>523</v>
+      </c>
+      <c r="G110" s="4" t="n">
+        <v>0.9388145315487572</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Metropolitano Oriente</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Isla de Pascua</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Hanga Roa (Isla De Pascua)</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>1.114285714285714</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Valparaíso San Antonio</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Claudio Vicuña (San Antonio)</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>458</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>483</v>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>0.94824016563147</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Valparaíso San Antonio</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Carlos Van Buren (Valparaíso)</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>574</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>633</v>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>0.9067930489731437</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Cabildo</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Víctor Hugo Moll (Cabildo)</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G114" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Calera</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Mario Sánchez Vergara (La Calera)</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G115" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>La Ligua</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Hospital San Agustín (La Ligua)</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G116" s="4" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Limache</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Santo Tomás (Limache)</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G117" s="4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Quillota</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Biprovincial Quillota Petorca</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>521</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>579</v>
+      </c>
+      <c r="G118" s="4" t="n">
+        <v>0.8998272884283247</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Quilpué</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Quilpué</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>196</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>417</v>
+      </c>
+      <c r="G119" s="4" t="n">
+        <v>0.4700239808153477</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Viña del Mar</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Gustavo Fricke (Viña del Mar)</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>779</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="G120" s="4" t="n">
+        <v>0.9164705882352941</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G121" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Clínico Herminda Martín (Chillán)</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>643</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>754</v>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>0.8527851458885941</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Comunitario de Salud Familiar de Quirihue</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>San Carlos</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de San Carlos</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>187</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>190</v>
+      </c>
+      <c r="G124" s="4" t="n">
+        <v>0.9842105263157894</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9"/>
+  <autoFilter ref="A1:G124"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/reporte_h2_RM_2026.xlsx
+++ b/output/reporte_h2_RM_2026.xlsx
@@ -15,8 +15,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Region'!$A$1:$D$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SS'!$A$1:$E$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comuna'!$A$1:$F$123</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Establecimiento'!$A$1:$G$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Comuna'!$A$1:$F$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Establecimiento'!$A$1:$G$130</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -494,13 +494,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1013</v>
+        <v>1214</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1712</v>
+        <v>2062</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.5917056074766355</v>
+        <v>0.588748787584869</v>
       </c>
     </row>
     <row r="3">
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>755</v>
+        <v>905</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>785</v>
+        <v>937</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.9617834394904459</v>
+        <v>0.9658484525080042</v>
       </c>
     </row>
     <row r="4">
@@ -526,13 +526,13 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>725</v>
+        <v>863</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>811</v>
+        <v>964</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.8939580764488286</v>
+        <v>0.8952282157676349</v>
       </c>
     </row>
     <row r="5">
@@ -542,13 +542,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>198</v>
+        <v>252</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>326</v>
+        <v>382</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.6073619631901841</v>
+        <v>0.6596858638743456</v>
       </c>
     </row>
     <row r="6">
@@ -558,13 +558,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2705</v>
+        <v>3264</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3033</v>
+        <v>3572</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.891856247939334</v>
+        <v>0.9137737961926092</v>
       </c>
     </row>
     <row r="7">
@@ -574,13 +574,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>1956</v>
+        <v>2403</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2120</v>
+        <v>2618</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.9226415094339623</v>
+        <v>0.9178762414056532</v>
       </c>
     </row>
     <row r="8">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>2077</v>
+        <v>2521</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2761</v>
+        <v>3349</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.7522636725823977</v>
+        <v>0.752762018512989</v>
       </c>
     </row>
     <row r="9">
@@ -606,13 +606,13 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1813</v>
+        <v>2145</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2124</v>
+        <v>2515</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.853578154425612</v>
+        <v>0.852882703777336</v>
       </c>
     </row>
     <row r="10">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2090</v>
+        <v>2418</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2294</v>
+        <v>2750</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.9110723626852659</v>
+        <v>0.8792727272727273</v>
       </c>
     </row>
     <row r="11">
@@ -638,13 +638,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>571</v>
+        <v>693</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>767</v>
+        <v>916</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.7444589308996089</v>
+        <v>0.7565502183406113</v>
       </c>
     </row>
     <row r="12">
@@ -654,13 +654,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>375</v>
+        <v>469</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>379</v>
+        <v>466</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.9894459102902374</v>
+        <v>1.006437768240343</v>
       </c>
     </row>
     <row r="13">
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>2910</v>
+        <v>3448</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3249</v>
+        <v>3859</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.8956602031394275</v>
+        <v>0.8934957242809017</v>
       </c>
     </row>
     <row r="14">
@@ -686,13 +686,13 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>12173</v>
+        <v>14386</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>13915</v>
+        <v>16469</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.8748113546532519</v>
+        <v>0.8735199465662761</v>
       </c>
     </row>
     <row r="15">
@@ -702,13 +702,13 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>908</v>
+        <v>1085</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1335</v>
+        <v>1619</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.6801498127340824</v>
+        <v>0.670166769610871</v>
       </c>
     </row>
     <row r="16">
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3327</v>
+        <v>3980</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>3808</v>
+        <v>4577</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.873686974789916</v>
+        <v>0.8695652173913043</v>
       </c>
     </row>
     <row r="17">
@@ -734,13 +734,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>838</v>
+        <v>1009</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>952</v>
+        <v>1134</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.8802521008403361</v>
+        <v>0.8897707231040565</v>
       </c>
     </row>
   </sheetData>
@@ -804,13 +804,13 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1013</v>
+        <v>1214</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1712</v>
+        <v>2062</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.5917056074766355</v>
+        <v>0.588748787584869</v>
       </c>
     </row>
     <row r="3">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>755</v>
+        <v>905</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>785</v>
+        <v>937</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.9617834394904459</v>
+        <v>0.9658484525080042</v>
       </c>
     </row>
     <row r="4">
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>725</v>
+        <v>863</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>811</v>
+        <v>964</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.8939580764488286</v>
+        <v>0.8952282157676349</v>
       </c>
     </row>
     <row r="5">
@@ -867,13 +867,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>198</v>
+        <v>252</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>326</v>
+        <v>382</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.6073619631901841</v>
+        <v>0.6596858638743456</v>
       </c>
     </row>
     <row r="6">
@@ -888,13 +888,13 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>293</v>
+        <v>354</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>376</v>
+        <v>450</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.7792553191489362</v>
+        <v>0.7866666666666666</v>
       </c>
     </row>
     <row r="7">
@@ -909,13 +909,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>870</v>
+        <v>1042</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>928</v>
+        <v>1093</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.9375</v>
+        <v>0.9533394327538883</v>
       </c>
     </row>
     <row r="8">
@@ -930,13 +930,13 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>922</v>
+        <v>1127</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1059</v>
+        <v>1236</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.8706326723323891</v>
+        <v>0.9118122977346278</v>
       </c>
     </row>
     <row r="9">
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>620</v>
+        <v>741</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>670</v>
+        <v>793</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.9253731343283582</v>
+        <v>0.9344262295081968</v>
       </c>
     </row>
     <row r="10">
@@ -972,13 +972,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1956</v>
+        <v>2403</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2120</v>
+        <v>2618</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.9226415094339623</v>
+        <v>0.9178762414056532</v>
       </c>
     </row>
     <row r="11">
@@ -993,13 +993,13 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>205</v>
+        <v>252</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>610</v>
+        <v>742</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.3360655737704918</v>
+        <v>0.3396226415094339</v>
       </c>
     </row>
     <row r="12">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1872</v>
+        <v>2269</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2151</v>
+        <v>2607</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.8702928870292888</v>
+        <v>0.8703490602224779</v>
       </c>
     </row>
     <row r="13">
@@ -1035,13 +1035,13 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1813</v>
+        <v>2145</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2124</v>
+        <v>2515</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.853578154425612</v>
+        <v>0.852882703777336</v>
       </c>
     </row>
     <row r="14">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>424</v>
+        <v>522</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>507</v>
+        <v>616</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.8362919132149902</v>
+        <v>0.8474025974025974</v>
       </c>
     </row>
     <row r="15">
@@ -1077,13 +1077,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1150</v>
+        <v>1288</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1195</v>
+        <v>1442</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.9623430962343096</v>
+        <v>0.8932038834951457</v>
       </c>
     </row>
     <row r="16">
@@ -1098,13 +1098,13 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>516</v>
+        <v>608</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>592</v>
+        <v>692</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.8716216216216216</v>
+        <v>0.8786127167630058</v>
       </c>
     </row>
     <row r="17">
@@ -1119,13 +1119,13 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>571</v>
+        <v>693</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>767</v>
+        <v>916</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.7444589308996089</v>
+        <v>0.7565502183406113</v>
       </c>
     </row>
     <row r="18">
@@ -1140,13 +1140,13 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>375</v>
+        <v>469</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>379</v>
+        <v>466</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.9894459102902374</v>
+        <v>1.006437768240343</v>
       </c>
     </row>
     <row r="19">
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2910</v>
+        <v>3448</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>3249</v>
+        <v>3859</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.8956602031394275</v>
+        <v>0.8934957242809017</v>
       </c>
     </row>
     <row r="20">
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2033</v>
+        <v>2350</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2195</v>
+        <v>2621</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.9261958997722096</v>
+        <v>0.8966043494849294</v>
       </c>
     </row>
     <row r="21">
@@ -1203,13 +1203,13 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1650</v>
+        <v>1940</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1885</v>
+        <v>2232</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.8753315649867374</v>
+        <v>0.8691756272401434</v>
       </c>
     </row>
     <row r="22">
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2505</v>
+        <v>2985</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>3018</v>
+        <v>3520</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.8300198807157058</v>
+        <v>0.8480113636363636</v>
       </c>
     </row>
     <row r="23">
@@ -1245,13 +1245,13 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1136</v>
+        <v>1357</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1224</v>
+        <v>1461</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.9281045751633987</v>
+        <v>0.9288158795345653</v>
       </c>
     </row>
     <row r="24">
@@ -1266,13 +1266,13 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>2320</v>
+        <v>2789</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>2614</v>
+        <v>3124</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.8875286916602907</v>
+        <v>0.8927656850192062</v>
       </c>
     </row>
     <row r="25">
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>2529</v>
+        <v>2965</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>2979</v>
+        <v>3511</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.8489425981873112</v>
+        <v>0.844488749643976</v>
       </c>
     </row>
     <row r="26">
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>908</v>
+        <v>1085</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1335</v>
+        <v>1619</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.6801498127340824</v>
+        <v>0.670166769610871</v>
       </c>
     </row>
     <row r="27">
@@ -1329,13 +1329,13 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>756</v>
+        <v>911</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>801</v>
+        <v>966</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.9438202247191011</v>
+        <v>0.943064182194617</v>
       </c>
     </row>
     <row r="28">
@@ -1350,13 +1350,13 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.114285714285714</v>
+        <v>1.093023255813953</v>
       </c>
     </row>
     <row r="29">
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1032</v>
+        <v>1248</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1116</v>
+        <v>1343</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.9247311827956989</v>
+        <v>0.9292628443782577</v>
       </c>
     </row>
     <row r="30">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1500</v>
+        <v>1774</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1856</v>
+        <v>2225</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.8081896551724138</v>
+        <v>0.7973033707865168</v>
       </c>
     </row>
     <row r="31">
@@ -1413,13 +1413,13 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>838</v>
+        <v>1009</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>952</v>
+        <v>1134</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.8802521008403361</v>
+        <v>0.8897707231040565</v>
       </c>
     </row>
   </sheetData>
@@ -1434,7 +1434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1494,13 +1494,13 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>465</v>
+        <v>565</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>994</v>
+        <v>1189</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>0.4678068410462777</v>
+        <v>0.4751892346509672</v>
       </c>
     </row>
     <row r="3">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>529</v>
+        <v>624</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>693</v>
+        <v>835</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0.7633477633477633</v>
+        <v>0.7473053892215569</v>
       </c>
     </row>
     <row r="4">
@@ -1546,13 +1546,13 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4285714285714285</v>
       </c>
     </row>
     <row r="5">
@@ -1568,17 +1568,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Taltal</t>
+          <t>San Pedro de Atacama</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1594,69 +1594,69 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Tocopilla</t>
+          <t>Taltal</t>
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.7058823529411765</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Arica Parinacota</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Arica y Parinacota</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Arica</t>
+          <t>Tocopilla</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>755</v>
+        <v>15</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>785</v>
+        <v>20</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.9617834394904459</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Arica Parinacota</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>Servicio de Salud Arica y Parinacota</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Chañaral</t>
+          <t>Arica</t>
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2</v>
+        <v>905</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1</v>
+        <v>937</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>2</v>
+        <v>0.9658484525080042</v>
       </c>
     </row>
     <row r="9">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Chañaral</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>494</v>
+        <v>2</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>575</v>
+        <v>2</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.8591304347826086</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1698,43 +1698,43 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Vallenar</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>229</v>
+        <v>593</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>235</v>
+        <v>685</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.9744680851063829</v>
+        <v>0.8656934306569343</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Aysén del General Carlos Ibañez del Campo</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Aysén</t>
+          <t>Servicio de Salud Atacama</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Aisén</t>
+          <t>Vallenar</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>11</v>
+        <v>268</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>16</v>
+        <v>277</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.6875</v>
+        <v>0.9675090252707581</v>
       </c>
     </row>
     <row r="12">
@@ -1750,16 +1750,18 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Chile Chico</t>
+          <t>Aisén</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.7222222222222222</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1774,18 +1776,16 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Cochrane</t>
+          <t>Chile Chico</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1800,43 +1800,43 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Coyhaique</t>
+          <t>Cochrane</t>
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>184</v>
+        <v>2</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>308</v>
+        <v>2</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.5974025974025974</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Aysén del General Carlos Ibañez del Campo</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Arauco</t>
+          <t>Servicio de Salud Aysén</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Cañete</t>
+          <t>Coyhaique</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>29</v>
+        <v>236</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>31</v>
+        <v>362</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.9354838709677419</v>
+        <v>0.6519337016574586</v>
       </c>
     </row>
     <row r="16">
@@ -1852,17 +1852,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Curanilahue</t>
+          <t>Cañete</t>
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>263</v>
+        <v>31</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>342</v>
+        <v>34</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.7690058479532164</v>
+        <v>0.9117647058823529</v>
       </c>
     </row>
     <row r="17">
@@ -1878,17 +1878,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Lebu</t>
+          <t>Curanilahue</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1</v>
+        <v>321</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>3</v>
+        <v>413</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.7772397094430993</v>
       </c>
     </row>
     <row r="18">
@@ -1899,22 +1899,22 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Biobío</t>
+          <t>Servicio de Salud Arauco</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Laja</t>
+          <t>Lebu</t>
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="19">
@@ -1930,17 +1930,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Los Ángeles</t>
+          <t>Laja</t>
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>866</v>
+        <v>1</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>919</v>
+        <v>2</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.9423286180631121</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Mulchén</t>
+          <t>Los Ángeles</t>
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1</v>
+        <v>1038</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>4</v>
+        <v>1083</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.25</v>
+        <v>0.9584487534626038</v>
       </c>
     </row>
     <row r="21">
@@ -1982,17 +1982,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Santa Bárbara</t>
+          <t>Mulchén</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="22">
@@ -2003,22 +2003,22 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Concepción</t>
+          <t>Servicio de Salud Biobío</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Santa Bárbara</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>710</v>
+        <v>2</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>801</v>
+        <v>4</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.8863920099875156</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="23">
@@ -2034,17 +2034,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Coronel</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>181</v>
+        <v>828</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>223</v>
+        <v>936</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.8116591928251121</v>
+        <v>0.8846153846153846</v>
       </c>
     </row>
     <row r="24">
@@ -2060,17 +2060,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Lota</t>
+          <t>Coronel</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>31</v>
+        <v>264</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>35</v>
+        <v>261</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.8857142857142857</v>
+        <v>1.011494252873563</v>
       </c>
     </row>
     <row r="25">
@@ -2081,22 +2081,22 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Talcahuano</t>
+          <t>Servicio de Salud Concepción</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Penco</t>
+          <t>Lota</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.75</v>
+        <v>0.8974358974358975</v>
       </c>
     </row>
     <row r="26">
@@ -2112,17 +2112,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Talcahuano</t>
+          <t>Penco</t>
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>613</v>
+        <v>3</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>661</v>
+        <v>4</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.9273827534039334</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="27">
@@ -2138,43 +2138,43 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Tome</t>
+          <t>Talcahuano</t>
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>4</v>
+        <v>734</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>5</v>
+        <v>784</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.8</v>
+        <v>0.9362244897959183</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo</t>
+          <t>Servicio de Salud Talcahuano</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Tome</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>786</v>
+        <v>4</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>827</v>
+        <v>5</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.9504232164449818</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="29">
@@ -2190,17 +2190,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Illapel</t>
+          <t>Andacollo</t>
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>126</v>
+        <v>1</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>168</v>
+        <v>1</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>579</v>
+        <v>933</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>611</v>
+        <v>1003</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.9476268412438625</v>
+        <v>0.9302093718843469</v>
       </c>
     </row>
     <row r="31">
@@ -2242,17 +2242,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Los Vilos</t>
+          <t>Illapel</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>12</v>
+        <v>157</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>10</v>
+        <v>206</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.2</v>
+        <v>0.7621359223300971</v>
       </c>
     </row>
     <row r="32">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Ovalle</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>440</v>
+        <v>727</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>489</v>
+        <v>767</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.8997955010224948</v>
+        <v>0.9478487614080835</v>
       </c>
     </row>
     <row r="33">
@@ -2294,17 +2294,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Salamanca</t>
+          <t>Los Vilos</t>
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.7777777777777778</v>
+        <v>1.153846153846154</v>
       </c>
     </row>
     <row r="34">
@@ -2320,66 +2320,66 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Vicuña</t>
+          <t>Ovalle</t>
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>6</v>
+        <v>556</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>6</v>
+        <v>612</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1</v>
+        <v>0.9084967320261438</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Norte</t>
+          <t>Servicio de Salud Coquimbo</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Angol</t>
+          <t>Salamanca</t>
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>332</v>
+        <v>10</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3343373493975904</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Norte</t>
+          <t>Servicio de Salud Coquimbo</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Collipulli</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F36" s="4" t="n">
         <v>1</v>
@@ -2398,17 +2398,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Lonquimay</t>
+          <t>Angol</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1</v>
+        <v>413</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>0</v>
+        <v>0.3462469733656174</v>
       </c>
     </row>
     <row r="38">
@@ -2424,17 +2424,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Traiguén</t>
+          <t>Collipulli</t>
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2450,17 +2450,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Lonquimay</t>
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>272</v>
+        <v>1</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>0.3419117647058824</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2471,22 +2471,22 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Araucanía Norte</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Carahue</t>
+          <t>Traiguén</t>
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2497,22 +2497,22 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Araucanía Norte</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Cunco</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1</v>
+        <v>321</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1</v>
+        <v>0.3364485981308411</v>
       </c>
     </row>
     <row r="42">
@@ -2528,17 +2528,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Galvarino</t>
+          <t>Carahue</t>
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2554,17 +2554,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Gorbea</t>
+          <t>Cunco</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2580,17 +2580,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Lautaro</t>
+          <t>Galvarino</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>0.5737704918032787</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="45">
@@ -2606,17 +2606,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Loncoche</t>
+          <t>Gorbea</t>
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -2632,17 +2632,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Nueva Imperial</t>
+          <t>Lautaro</t>
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>0.9836065573770492</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="47">
@@ -2658,14 +2658,14 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Pitrufquén</t>
+          <t>Loncoche</t>
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="F47" s="4" t="n">
         <v>1</v>
@@ -2684,17 +2684,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Pucón</t>
+          <t>Nueva Imperial</t>
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1</v>
+        <v>0.9876543209876543</v>
       </c>
     </row>
     <row r="49">
@@ -2710,17 +2710,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Pitrufquén</t>
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Temuco</t>
+          <t>Pucón</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>1335</v>
+        <v>14</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>1558</v>
+        <v>14</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>0.8568677792041078</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -2762,17 +2762,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Toltén</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -2788,69 +2788,69 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Villarrica</t>
+          <t>Temuco</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>373</v>
+        <v>1610</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>397</v>
+        <v>1870</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>0.9395465994962217</v>
+        <v>0.8609625668449198</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Araucanía Sur</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Graneros</t>
+          <t>Toltén</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Araucanía Sur</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Lolol</t>
+          <t>Villarrica</t>
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>0</v>
+        <v>466</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>2</v>
+        <v>493</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>0</v>
+        <v>0.9452332657200812</v>
       </c>
     </row>
     <row r="55">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Nancagua</t>
+          <t>Graneros</t>
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="56">
@@ -2892,17 +2892,17 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Peumo</t>
+          <t>Lolol</t>
         </is>
       </c>
       <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E56" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="F56" s="4" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Pichidegua</t>
+          <t>Nancagua</t>
         </is>
       </c>
       <c r="D57" s="3" t="n">
@@ -2944,17 +2944,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
+          <t>Peumo</t>
         </is>
       </c>
       <c r="D58" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E58" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="59">
@@ -2970,17 +2970,17 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Rancagua</t>
+          <t>Pichidegua</t>
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>836</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>1018</v>
+        <v>1</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>0.8212180746561886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2996,17 +2996,17 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Rengo</t>
+          <t>Pichilemu</t>
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>336</v>
+        <v>3</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>401</v>
+        <v>6</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>0.8379052369077307</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="61">
@@ -3022,17 +3022,17 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>San Fernando</t>
+          <t>Rancagua</t>
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>315</v>
+        <v>996</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>349</v>
+        <v>1215</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>0.9025787965616046</v>
+        <v>0.8197530864197531</v>
       </c>
     </row>
     <row r="62">
@@ -3048,17 +3048,17 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>Rengo</t>
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>23</v>
+        <v>390</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>27</v>
+        <v>466</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>0.8518518518518519</v>
+        <v>0.8369098712446352</v>
       </c>
     </row>
     <row r="63">
@@ -3074,69 +3074,69 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>San Fernando</t>
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>298</v>
+        <v>371</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>314</v>
+        <v>412</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>0.9490445859872612</v>
+        <v>0.9004854368932039</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Chiloé</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Ancud</t>
+          <t>San Vicente</t>
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>0.8</v>
+        <v>0.8709677419354839</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Chiloé</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Castro</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>270</v>
+        <v>355</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.9491978609625669</v>
       </c>
     </row>
     <row r="66">
@@ -3152,17 +3152,17 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Quellón</t>
+          <t>Ancud</t>
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>0.8045977011494253</v>
+        <v>0.7637795275590551</v>
       </c>
     </row>
     <row r="67">
@@ -3173,22 +3173,22 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Reloncaví</t>
+          <t>Servicio de Salud Chiloé</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Calbuco</t>
+          <t>Castro</t>
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>2</v>
+        <v>335</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>3</v>
+        <v>381</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8792650918635171</v>
       </c>
     </row>
     <row r="68">
@@ -3199,21 +3199,23 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Reloncaví</t>
+          <t>Servicio de Salud Chiloé</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Frutillar</t>
+          <t>Quellón</t>
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="4" t="n"/>
+        <v>108</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>0.8333333333333334</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3228,17 +3230,17 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Calbuco</t>
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>1147</v>
+        <v>2</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>1192</v>
+        <v>3</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>0.962248322147651</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="70">
@@ -3249,100 +3251,96 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Osorno</t>
+          <t>Servicio de Salud Del Reloncaví</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Osorno</t>
+          <t>Frutillar</t>
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>516</v>
+        <v>1</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>592</v>
-      </c>
-      <c r="F70" s="4" t="n">
-        <v>0.8716216216216216</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Los Rios</t>
+          <t>Servicio de Salud Del Reloncaví</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>La Unión</t>
+          <t>Futaleufú</t>
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="F71" s="4" t="n">
-        <v>0.7777777777777778</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Los Rios</t>
+          <t>Servicio de Salud Del Reloncaví</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Lanco</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>1</v>
+        <v>1284</v>
       </c>
       <c r="E72" s="3" t="n">
-        <v>1</v>
+        <v>1439</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1</v>
+        <v>0.8922863099374566</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Los Rios</t>
+          <t>Servicio de Salud Osorno</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>6</v>
+        <v>608</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>6</v>
+        <v>692</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1</v>
+        <v>0.8786127167630058</v>
       </c>
     </row>
     <row r="74">
@@ -3358,17 +3356,17 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Mariquina</t>
+          <t>La Unión</t>
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>0.9</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="75">
@@ -3384,17 +3382,17 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Paillaco</t>
+          <t>Lanco</t>
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -3410,17 +3408,17 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Panguipulli</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -3436,17 +3434,17 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Río Bueno</t>
+          <t>Mariquina</t>
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>0.6</v>
+        <v>0.9230769230769231</v>
       </c>
     </row>
     <row r="78">
@@ -3462,147 +3460,147 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Valdivia</t>
+          <t>Paillaco</t>
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>516</v>
+        <v>13</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>697</v>
+        <v>16</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>0.7403156384505022</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Magallanes y de la Antártica Chilena</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Magallanes</t>
+          <t>Servicio de Salud Los Rios</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Natales</t>
+          <t>Panguipulli</t>
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>0.958904109589041</v>
+        <v>0.6111111111111112</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Magallanes y de la Antártica Chilena</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Magallanes</t>
+          <t>Servicio de Salud Los Rios</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Punta Arenas</t>
+          <t>Río Bueno</t>
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>305</v>
+        <v>4</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>306</v>
+        <v>6</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>0.9967320261437909</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Los Rios</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
+          <t>Valdivia</t>
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>37</v>
+        <v>628</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>42</v>
+        <v>834</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>0.8809523809523809</v>
+        <v>0.7529976019184652</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Magallanes y de la Antártica Chilena</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Magallanes</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Constitución</t>
+          <t>Natales</t>
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>0.75</v>
+        <v>0.9666666666666667</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Magallanes y de la Antártica Chilena</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Magallanes</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Curicó</t>
+          <t>Punta Arenas</t>
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>847</v>
+        <v>382</v>
       </c>
       <c r="E83" s="3" t="n">
-        <v>877</v>
+        <v>376</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>0.9657924743443558</v>
+        <v>1.015957446808511</v>
       </c>
     </row>
     <row r="84">
@@ -3618,17 +3616,17 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Licantén</t>
+          <t>Cauquenes</t>
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>0</v>
+        <v>0.8867924528301887</v>
       </c>
     </row>
     <row r="85">
@@ -3644,17 +3642,17 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Linares</t>
+          <t>Constitución</t>
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>476</v>
+        <v>19</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>588</v>
+        <v>24</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="86">
@@ -3670,17 +3668,17 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Parral</t>
+          <t>Curepto</t>
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>0.5319148936170213</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="87">
@@ -3696,17 +3694,17 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>San Javier</t>
+          <t>Curicó</t>
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>18</v>
+        <v>1012</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>32</v>
+        <v>1048</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>0.5625</v>
+        <v>0.9656488549618321</v>
       </c>
     </row>
     <row r="88">
@@ -3722,121 +3720,121 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>Licantén</t>
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>1492</v>
+        <v>0</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>1642</v>
+        <v>1</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>0.9086479902557856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Central</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>Linares</t>
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>925</v>
+        <v>558</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>955</v>
+        <v>693</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>0.9685863874345549</v>
+        <v>0.8051948051948052</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Central</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Parral</t>
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>1108</v>
+        <v>27</v>
       </c>
       <c r="E90" s="3" t="n">
-        <v>1240</v>
+        <v>57</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>0.8935483870967742</v>
+        <v>0.4736842105263158</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Norte</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Colina</t>
+          <t>San Javier</t>
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>0</v>
+        <v>0.4883720930232558</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Norte</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Independencia</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1650</v>
+        <v>1763</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>1881</v>
+        <v>1938</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>0.8771929824561403</v>
+        <v>0.9097007223942208</v>
       </c>
     </row>
     <row r="93">
@@ -3847,22 +3845,22 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Occidente</t>
+          <t>Servicio de Salud Metropolitano Central</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Cerro Navia</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>951</v>
+        <v>1022</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>1090</v>
+        <v>1140</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>0.8724770642201835</v>
+        <v>0.8964912280701754</v>
       </c>
     </row>
     <row r="94">
@@ -3873,22 +3871,22 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Occidente</t>
+          <t>Servicio de Salud Metropolitano Central</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Melipilla</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>472</v>
+        <v>1328</v>
       </c>
       <c r="E94" s="3" t="n">
-        <v>571</v>
+        <v>1481</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>0.8266199649737302</v>
+        <v>0.8966914247130318</v>
       </c>
     </row>
     <row r="95">
@@ -3899,22 +3897,22 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Occidente</t>
+          <t>Servicio de Salud Metropolitano Norte</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Peñaflor</t>
+          <t>Colina</t>
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -3925,22 +3923,22 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Occidente</t>
+          <t>Servicio de Salud Metropolitano Norte</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>910</v>
+        <v>1940</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>931</v>
+        <v>2228</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>0.9774436090225563</v>
+        <v>0.8707360861759426</v>
       </c>
     </row>
     <row r="97">
@@ -3956,17 +3954,17 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Talagante</t>
+          <t>Cerro Navia</t>
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>155</v>
+        <v>1164</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>402</v>
+        <v>1308</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>0.3855721393034826</v>
+        <v>0.8899082568807339</v>
       </c>
     </row>
     <row r="98">
@@ -3977,22 +3975,22 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Oriente</t>
+          <t>Servicio de Salud Metropolitano Occidente</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Peñalolén</t>
+          <t>Melipilla</t>
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>1136</v>
+        <v>581</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>1224</v>
+        <v>684</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>0.9281045751633987</v>
+        <v>0.8494152046783626</v>
       </c>
     </row>
     <row r="99">
@@ -4003,22 +4001,22 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur</t>
+          <t>Servicio de Salud Metropolitano Occidente</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Buin</t>
+          <t>Peñaflor</t>
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>281</v>
+        <v>23</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>306</v>
+        <v>32</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>0.9183006535947712</v>
+        <v>0.71875</v>
       </c>
     </row>
     <row r="100">
@@ -4029,22 +4027,22 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur</t>
+          <t>Servicio de Salud Metropolitano Occidente</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>1226</v>
+        <v>1062</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>1289</v>
+        <v>1094</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>0.9511249030256013</v>
+        <v>0.9707495429616088</v>
       </c>
     </row>
     <row r="101">
@@ -4055,22 +4053,22 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur</t>
+          <t>Servicio de Salud Metropolitano Occidente</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Talagante</t>
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>813</v>
+        <v>155</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>1019</v>
+        <v>402</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>0.7978410206084396</v>
+        <v>0.3855721393034826</v>
       </c>
     </row>
     <row r="102">
@@ -4081,22 +4079,22 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Oriente</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>La Florida</t>
+          <t>Peñalolén</t>
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>750</v>
+        <v>1357</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>898</v>
+        <v>1461</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>0.8351893095768375</v>
+        <v>0.9288158795345653</v>
       </c>
     </row>
     <row r="103">
@@ -4107,22 +4105,22 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
+          <t>Buin</t>
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>1025</v>
+        <v>338</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>1264</v>
+        <v>366</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>0.8109177215189873</v>
+        <v>0.9234972677595629</v>
       </c>
     </row>
     <row r="104">
@@ -4133,178 +4131,178 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>San Ramón</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>754</v>
+        <v>1468</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>817</v>
+        <v>1545</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>0.9228886168910648</v>
+        <v>0.9501618122977347</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Tarapacá</t>
+          <t>Servicio de Salud Metropolitano Sur</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Alto Hospicio</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>18</v>
+        <v>983</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>19</v>
+        <v>1213</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.8103874690849134</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Tarapacá</t>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Iquique</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>890</v>
+        <v>902</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>1316</v>
+        <v>1061</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>0.6762917933130699</v>
+        <v>0.8501413760603205</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Aconcagua</t>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Llaillay</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>1185</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>2</v>
+        <v>1494</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>0</v>
+        <v>0.7931726907630522</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Aconcagua</t>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Ramón</t>
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>265</v>
+        <v>878</v>
       </c>
       <c r="E108" s="3" t="n">
-        <v>276</v>
+        <v>956</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>0.9601449275362319</v>
+        <v>0.9184100418410042</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Aconcagua</t>
+          <t>Servicio de Salud Tarapacá</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>San Felipe</t>
+          <t>Alto Hospicio</t>
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>491</v>
+        <v>31</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>523</v>
+        <v>31</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>0.9388145315487572</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Oriente</t>
+          <t>Servicio de Salud Tarapacá</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Isla de Pascua</t>
+          <t>Iquique</t>
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>39</v>
+        <v>1054</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>35</v>
+        <v>1588</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1.114285714285714</v>
+        <v>0.663727959697733</v>
       </c>
     </row>
     <row r="111">
@@ -4315,22 +4313,22 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Valparaíso San Antonio</t>
+          <t>Servicio de Salud Aconcagua</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Llaillay</t>
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>458</v>
+        <v>0</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>483</v>
+        <v>2</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>0.94824016563147</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -4341,22 +4339,22 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Valparaíso San Antonio</t>
+          <t>Servicio de Salud Aconcagua</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>574</v>
+        <v>331</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>633</v>
+        <v>344</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>0.9067930489731437</v>
+        <v>0.9622093023255814</v>
       </c>
     </row>
     <row r="113">
@@ -4367,22 +4365,22 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
+          <t>Servicio de Salud Aconcagua</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Cabildo</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>2</v>
+        <v>620</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>0.5</v>
+        <v>0.9354838709677419</v>
       </c>
     </row>
     <row r="114">
@@ -4393,22 +4391,22 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
+          <t>Servicio de Salud Metropolitano Oriente</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Calera</t>
+          <t>Isla de Pascua</t>
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>0.5</v>
+        <v>1.093023255813953</v>
       </c>
     </row>
     <row r="115">
@@ -4419,22 +4417,22 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
+          <t>Servicio de Salud Valparaíso San Antonio</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>La Ligua</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>1</v>
+        <v>550</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>4</v>
+        <v>579</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>0.25</v>
+        <v>0.9499136442141624</v>
       </c>
     </row>
     <row r="116">
@@ -4445,22 +4443,22 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
+          <t>Servicio de Salud Valparaíso San Antonio</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Limache</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>1</v>
+        <v>698</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>2</v>
+        <v>764</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>0.5</v>
+        <v>0.9136125654450262</v>
       </c>
     </row>
     <row r="117">
@@ -4476,17 +4474,17 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Quillota</t>
+          <t>Cabildo</t>
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>521</v>
+        <v>2</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>579</v>
+        <v>3</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>0.8998272884283247</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="118">
@@ -4502,17 +4500,17 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Quilpué</t>
+          <t>Calera</t>
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>196</v>
+        <v>2</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>417</v>
+        <v>4</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>0.4700239808153477</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="119">
@@ -4528,125 +4526,255 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Viña del Mar</t>
+          <t>La Ligua</t>
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>779</v>
+        <v>3</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>850</v>
+        <v>6</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>0.9164705882352941</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Ñuble</t>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Bulnes</t>
+          <t>Limache</t>
         </is>
       </c>
       <c r="D120" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Ñuble</t>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Chillán</t>
+          <t>Quillota</t>
         </is>
       </c>
       <c r="D121" s="3" t="n">
-        <v>643</v>
+        <v>606</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>754</v>
+        <v>676</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>0.8527851458885941</v>
+        <v>0.8964497041420119</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Ñuble</t>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Quirihue</t>
+          <t>Quilpué</t>
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>6</v>
+        <v>237</v>
       </c>
       <c r="E122" s="3" t="n">
-        <v>6</v>
+        <v>502</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1</v>
+        <v>0.4721115537848606</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Quintero</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Viña del Mar</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>922</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>1030</v>
+      </c>
+      <c r="F124" s="4" t="n">
+        <v>0.8951456310679612</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
           <t>Ñuble</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>Servicio de Salud Ñuble</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>782</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>904</v>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>0.8650442477876106</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F127" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
         <is>
           <t>San Carlos</t>
         </is>
       </c>
-      <c r="D123" s="3" t="n">
-        <v>187</v>
-      </c>
-      <c r="E123" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="F123" s="4" t="n">
-        <v>0.9842105263157894</v>
+      <c r="D128" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="F128" s="4" t="n">
+        <v>0.9863636363636363</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F123"/>
+  <autoFilter ref="A1:F128"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4657,7 +4785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4728,13 +4856,13 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>465</v>
+        <v>565</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>994</v>
+        <v>1189</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.4678068410462777</v>
+        <v>0.4751892346509672</v>
       </c>
     </row>
     <row r="3">
@@ -4759,13 +4887,13 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>529</v>
+        <v>624</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>693</v>
+        <v>835</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.7633477633477633</v>
+        <v>0.7473053892215569</v>
       </c>
     </row>
     <row r="4">
@@ -4790,13 +4918,13 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.4285714285714285</v>
       </c>
     </row>
     <row r="5">
@@ -4812,22 +4940,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Taltal</t>
+          <t>San Pedro de Atacama</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Hospital 21 de Mayo (Taltal)</t>
+          <t>Centro de Salud Familiar San Pedro Atacama</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4843,84 +4971,84 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Tocopilla</t>
+          <t>Taltal</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Marcos Macuada (Tocopilla)</t>
+          <t>Hospital 21 de Mayo (Taltal)</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.7058823529411765</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Arica Parinacota</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Arica y Parinacota</t>
+          <t>Servicio de Salud Antofagasta</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Arica</t>
+          <t>Tocopilla</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Hospital Regional Dr. Juan Noé Crevani (Arica)</t>
+          <t>Hospital Dr. Marcos Macuada (Tocopilla)</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>755</v>
+        <v>15</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>785</v>
+        <v>20</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.9617834394904459</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Arica Parinacota</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>Servicio de Salud Arica y Parinacota</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Chañaral</t>
+          <t>Arica</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Jerónimo Méndez Arancibia (Chañaral)</t>
+          <t>Hospital Regional Dr. Juan Noé Crevani (Arica)</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2</v>
+        <v>905</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1</v>
+        <v>937</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2</v>
+        <v>0.9658484525080042</v>
       </c>
     </row>
     <row r="9">
@@ -4936,22 +5064,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Chañaral</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Hospital San José del Carmen (Copiapó)</t>
+          <t>Hospital Dr. Jerónimo Méndez Arancibia (Chañaral)</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>494</v>
+        <v>2</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>575</v>
+        <v>2</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.8591304347826086</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -4967,53 +5095,53 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Vallenar</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Hospital Provincial del Huasco Monseñor Fernando Ariztía Ruiz (Vallenar)</t>
+          <t>Hospital San José del Carmen (Copiapó)</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>229</v>
+        <v>593</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>235</v>
+        <v>685</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.9744680851063829</v>
+        <v>0.8656934306569343</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Aysén del General Carlos Ibañez del Campo</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Aysén</t>
+          <t>Servicio de Salud Atacama</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Aisén</t>
+          <t>Vallenar</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Puerto Aysén</t>
+          <t>Hospital Provincial del Huasco Monseñor Fernando Ariztía Ruiz (Vallenar)</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>11</v>
+        <v>268</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>16</v>
+        <v>277</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.6875</v>
+        <v>0.9675090252707581</v>
       </c>
     </row>
     <row r="12">
@@ -5029,21 +5157,23 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Chile Chico</t>
+          <t>Aisén</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Leopoldo Ortega Rodríguez (Chile Chico)</t>
+          <t>Hospital de Puerto Aysén</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="4" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0.7222222222222222</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -5058,23 +5188,21 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Cochrane</t>
+          <t>Chile Chico</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Hospital Lord Cochrane</t>
+          <t>Hospital Dr. Leopoldo Ortega Rodríguez (Chile Chico)</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -5089,53 +5217,53 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Coyhaique</t>
+          <t>Cochrane</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Hospital Regional de Coyhaique</t>
+          <t>Hospital Lord Cochrane</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>184</v>
+        <v>2</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>308</v>
+        <v>2</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.5974025974025974</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Aysén del General Carlos Ibañez del Campo</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Arauco</t>
+          <t>Servicio de Salud Aysén</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Cañete</t>
+          <t>Coyhaique</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Hospital Intercultural Kallvu Llanka (Cañete)</t>
+          <t>Hospital Regional de Coyhaique</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>29</v>
+        <v>236</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>31</v>
+        <v>362</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.9354838709677419</v>
+        <v>0.6519337016574586</v>
       </c>
     </row>
     <row r="16">
@@ -5151,22 +5279,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Curanilahue</t>
+          <t>Cañete</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Hospital Provincial Dr. Rafael Avaría (Curanilahue)</t>
+          <t>Hospital Intercultural Kallvu Llanka (Cañete)</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>263</v>
+        <v>31</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>342</v>
+        <v>34</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.7690058479532164</v>
+        <v>0.9117647058823529</v>
       </c>
     </row>
     <row r="17">
@@ -5182,22 +5310,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Lebu</t>
+          <t>Curanilahue</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Lebu</t>
+          <t>Hospital Provincial Dr. Rafael Avaría (Curanilahue)</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1</v>
+        <v>321</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3</v>
+        <v>413</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.7772397094430993</v>
       </c>
     </row>
     <row r="18">
@@ -5208,27 +5336,27 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Biobío</t>
+          <t>Servicio de Salud Arauco</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Laja</t>
+          <t>Lebu</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Laja</t>
+          <t>Hospital de Lebu</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="19">
@@ -5244,22 +5372,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Los Ángeles</t>
+          <t>Laja</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Complejo Asistencial Dr. Víctor Ríos Ruiz (Los Ángeles)</t>
+          <t>Hospital Comunitario de Laja</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>866</v>
+        <v>1</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>919</v>
+        <v>2</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.9423286180631121</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
@@ -5275,22 +5403,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Mulchén</t>
+          <t>Los Ángeles</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Mulchén</t>
+          <t>Complejo Asistencial Dr. Víctor Ríos Ruiz (Los Ángeles)</t>
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1</v>
+        <v>1038</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>4</v>
+        <v>1083</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.25</v>
+        <v>0.9584487534626038</v>
       </c>
     </row>
     <row r="21">
@@ -5306,22 +5434,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Santa Bárbara</t>
+          <t>Mulchén</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Santa Bárbara</t>
+          <t>Hospital de Mulchén</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="22">
@@ -5332,27 +5460,27 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Concepción</t>
+          <t>Servicio de Salud Biobío</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Santa Bárbara</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Hospital Clínico Regional Dr. Guillermo Grant Benavente (Concepción)</t>
+          <t>Hospital Comunitario de Santa Bárbara</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>710</v>
+        <v>2</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>801</v>
+        <v>4</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.8863920099875156</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="23">
@@ -5368,22 +5496,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Coronel</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Hospital San José (Coronel)</t>
+          <t>Hospital Clínico Regional Dr. Guillermo Grant Benavente (Concepción)</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>181</v>
+        <v>828</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>223</v>
+        <v>936</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.8116591928251121</v>
+        <v>0.8846153846153846</v>
       </c>
     </row>
     <row r="24">
@@ -5399,22 +5527,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Lota</t>
+          <t>Coronel</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Lota</t>
+          <t>Hospital San José (Coronel)</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>31</v>
+        <v>264</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>35</v>
+        <v>261</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.8857142857142857</v>
+        <v>1.011494252873563</v>
       </c>
     </row>
     <row r="25">
@@ -5425,27 +5553,27 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Talcahuano</t>
+          <t>Servicio de Salud Concepción</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Penco</t>
+          <t>Lota</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Hospital Penco Lirquén</t>
+          <t>Hospital de Lota</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.75</v>
+        <v>0.8974358974358975</v>
       </c>
     </row>
     <row r="26">
@@ -5461,22 +5589,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Talcahuano</t>
+          <t>Penco</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Hospital Las Higueras (Talcahuano)</t>
+          <t>Hospital Penco Lirquén</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>613</v>
+        <v>3</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>661</v>
+        <v>4</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.9273827534039334</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="27">
@@ -5492,53 +5620,53 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Tome</t>
+          <t>Talcahuano</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Tomé</t>
+          <t>Hospital Las Higueras (Talcahuano)</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>4</v>
+        <v>734</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>5</v>
+        <v>784</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.8</v>
+        <v>0.9362244897959183</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo</t>
+          <t>Servicio de Salud Talcahuano</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Tome</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Pablo (Coquimbo)</t>
+          <t>Hospital de Tomé</t>
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>786</v>
+        <v>4</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>827</v>
+        <v>5</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.9504232164449818</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="29">
@@ -5554,22 +5682,22 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Illapel</t>
+          <t>Andacollo</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Humberto Elorza Cortés (Illapel)</t>
+          <t>Hospital Dr. José Arraño (Andacollo)</t>
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>126</v>
+        <v>1</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>168</v>
+        <v>1</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -5585,22 +5713,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios (La Serena)</t>
+          <t>Hospital San Pablo (Coquimbo)</t>
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>579</v>
+        <v>933</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>611</v>
+        <v>1003</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.9476268412438625</v>
+        <v>0.9302093718843469</v>
       </c>
     </row>
     <row r="31">
@@ -5616,22 +5744,22 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Los Vilos</t>
+          <t>Illapel</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Pedro (Los Vilos)</t>
+          <t>Hospital Dr. Humberto Elorza Cortés (Illapel)</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>12</v>
+        <v>157</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>10</v>
+        <v>206</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.2</v>
+        <v>0.7621359223300971</v>
       </c>
     </row>
     <row r="32">
@@ -5647,22 +5775,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Ovalle</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Antonio Tirado Lanas de Ovalle</t>
+          <t>Hospital San Juan de Dios (La Serena)</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>440</v>
+        <v>727</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>489</v>
+        <v>767</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.8997955010224948</v>
+        <v>0.9478487614080835</v>
       </c>
     </row>
     <row r="33">
@@ -5678,22 +5806,22 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Salamanca</t>
+          <t>Los Vilos</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Salamanca</t>
+          <t>Hospital San Pedro (Los Vilos)</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.7777777777777778</v>
+        <v>1.153846153846154</v>
       </c>
     </row>
     <row r="34">
@@ -5709,81 +5837,81 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Vicuña</t>
+          <t>Ovalle</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios (Vicuña)</t>
+          <t>Hospital Dr. Antonio Tirado Lanas de Ovalle</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>6</v>
+        <v>556</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>6</v>
+        <v>612</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>1</v>
+        <v>0.9084967320261438</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Norte</t>
+          <t>Servicio de Salud Coquimbo</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Angol</t>
+          <t>Salamanca</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Mauricio Heyermann (Angol)</t>
+          <t>Hospital de Salamanca</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>332</v>
+        <v>10</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.3343373493975904</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Norte</t>
+          <t>Servicio de Salud Coquimbo</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Collipulli</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Collipulli</t>
+          <t>Hospital San Juan de Dios (Vicuña)</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G36" s="4" t="n">
         <v>1</v>
@@ -5802,22 +5930,22 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Lonquimay</t>
+          <t>Angol</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Lonquimay</t>
+          <t>Hospital Dr. Mauricio Heyermann (Angol)</t>
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0</v>
+        <v>143</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>1</v>
+        <v>413</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>0</v>
+        <v>0.3462469733656174</v>
       </c>
     </row>
     <row r="38">
@@ -5833,22 +5961,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Traiguén</t>
+          <t>Collipulli</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Dino Stagno M.(Traiguén)</t>
+          <t>Hospital de Collipulli</t>
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -5864,22 +5992,22 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Lonquimay</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Hospital San José de Victoria</t>
+          <t>Hospital de Lonquimay</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>272</v>
+        <v>1</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>0.3419117647058824</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -5890,27 +6018,27 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Araucanía Norte</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Carahue</t>
+          <t>Traiguén</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Hospital Familiar y Comunitario Carahue</t>
+          <t>Hospital Dr. Dino Stagno M.(Traiguén)</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -5921,27 +6049,27 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Araucanía Sur</t>
+          <t>Servicio de Salud Araucanía Norte</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Cunco</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Eduardo González Galeno (Cunco)</t>
+          <t>Hospital San José de Victoria</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>1</v>
+        <v>321</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>1</v>
+        <v>0.3364485981308411</v>
       </c>
     </row>
     <row r="42">
@@ -5957,22 +6085,22 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Galvarino</t>
+          <t>Carahue</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Galvarino</t>
+          <t>Hospital Familiar y Comunitario Carahue</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -5988,22 +6116,22 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Gorbea</t>
+          <t>Cunco</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Gorbea</t>
+          <t>Hospital Dr. Eduardo González Galeno (Cunco)</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -6019,22 +6147,22 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Lautaro</t>
+          <t>Galvarino</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Abraham Godoy Peña (Lautaro)</t>
+          <t>Hospital de Galvarino</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>0.5737704918032787</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="45">
@@ -6050,22 +6178,22 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Loncoche</t>
+          <t>Gorbea</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Hospital Familiar y Comunitario de Loncoche</t>
+          <t>Hospital de Gorbea</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F45" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -6081,22 +6209,22 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Nueva Imperial</t>
+          <t>Lautaro</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Hospital Intercultural de Nueva Imperial</t>
+          <t>Hospital Dr. Abraham Godoy Peña (Lautaro)</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>0.9836065573770492</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="47">
@@ -6112,19 +6240,19 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Pitrufquén</t>
+          <t>Loncoche</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Pitrufquén</t>
+          <t>Hospital Familiar y Comunitario de Loncoche</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="G47" s="4" t="n">
         <v>1</v>
@@ -6143,22 +6271,22 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Pucón</t>
+          <t>Nueva Imperial</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Francisco de Pucón (D)</t>
+          <t>Hospital Intercultural de Nueva Imperial</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>1</v>
+        <v>0.9876543209876543</v>
       </c>
     </row>
     <row r="49">
@@ -6174,22 +6302,22 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Saavedra</t>
+          <t>Pitrufquén</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Arturo Hillerns Larrañaga (Saavedra)</t>
+          <t>Hospital de Pitrufquén</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -6205,22 +6333,22 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Temuco</t>
+          <t>Pucón</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Hernán Henríquez Aravena (Temuco)</t>
+          <t>Hospital San Francisco de Pucón (D)</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>1335</v>
+        <v>14</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>1558</v>
+        <v>14</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>0.8568677792041078</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -6236,22 +6364,22 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Toltén</t>
+          <t>Saavedra</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Toltén</t>
+          <t>Hospital Dr. Arturo Hillerns Larrañaga (Saavedra)</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -6267,84 +6395,84 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Villarrica</t>
+          <t>Temuco</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Villarrica</t>
+          <t>Hospital Dr. Hernán Henríquez Aravena (Temuco)</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>373</v>
+        <v>1610</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>397</v>
+        <v>1870</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>0.9395465994962217</v>
+        <v>0.8609625668449198</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Araucanía Sur</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Graneros</t>
+          <t>Toltén</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Hospital Santa Filomena de Graneros</t>
+          <t>Hospital de Toltén</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Libertador Gral. B. O'Higgins</t>
+          <t>La Araucanía</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
+          <t>Servicio de Salud Araucanía Sur</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Lolol</t>
+          <t>Villarrica</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Lolol</t>
+          <t>Hospital de Villarrica</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>0</v>
+        <v>466</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>2</v>
+        <v>493</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>0</v>
+        <v>0.9452332657200812</v>
       </c>
     </row>
     <row r="55">
@@ -6360,22 +6488,22 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Nancagua</t>
+          <t>Graneros</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Nancagua</t>
+          <t>Hospital Santa Filomena de Graneros</t>
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="56">
@@ -6391,22 +6519,22 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Peumo</t>
+          <t>Lolol</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Hospital Del Salvador de Peumo</t>
+          <t>Hospital de Lolol</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F56" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="G56" s="4" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -6422,12 +6550,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Pichidegua</t>
+          <t>Nancagua</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Pichidegua</t>
+          <t>Hospital de Nancagua</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
@@ -6453,22 +6581,22 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
+          <t>Peumo</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Pichilemu</t>
+          <t>Hospital Del Salvador de Peumo</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="59">
@@ -6484,22 +6612,22 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Rancagua</t>
+          <t>Pichidegua</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Franco Ravera Zunino</t>
+          <t>Hospital de Pichidegua</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>836</v>
+        <v>0</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>1018</v>
+        <v>1</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>0.8212180746561886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -6515,22 +6643,22 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Rengo</t>
+          <t>Pichilemu</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Ricardo Valenzuela Sáez (Rengo)</t>
+          <t>Hospital de Pichilemu</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>336</v>
+        <v>3</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>401</v>
+        <v>6</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>0.8379052369077307</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="61">
@@ -6546,22 +6674,22 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>San Fernando</t>
+          <t>Rancagua</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios de San Fernando</t>
+          <t>Hospital Dr. Franco Ravera Zunino</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>315</v>
+        <v>996</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>349</v>
+        <v>1215</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>0.9025787965616046</v>
+        <v>0.8197530864197531</v>
       </c>
     </row>
     <row r="62">
@@ -6577,22 +6705,22 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>Rengo</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Vicente de Tagua -Tagua</t>
+          <t>Hospital Dr. Ricardo Valenzuela Sáez (Rengo)</t>
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>23</v>
+        <v>390</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>27</v>
+        <v>466</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>0.8518518518518519</v>
+        <v>0.8369098712446352</v>
       </c>
     </row>
     <row r="63">
@@ -6608,84 +6736,84 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>San Fernando</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Santa Cruz</t>
+          <t>Hospital San Juan de Dios de San Fernando</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>298</v>
+        <v>371</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>314</v>
+        <v>412</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>0.9490445859872612</v>
+        <v>0.9004854368932039</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Chiloé</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Ancud</t>
+          <t>San Vicente</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Ancud</t>
+          <t>Hospital San Vicente de Tagua -Tagua</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>0.8</v>
+        <v>0.8709677419354839</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Libertador Gral. B. O'Higgins</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Chiloé</t>
+          <t>Servicio de Salud Del Libertador B.O'Higgins</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Castro</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>Hospital de Santa Cruz</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>270</v>
+        <v>355</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>315</v>
+        <v>374</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.9491978609625669</v>
       </c>
     </row>
     <row r="66">
@@ -6701,22 +6829,22 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Quellón</t>
+          <t>Ancud</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Quellón</t>
+          <t>Hospital de Ancud</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>0.8045977011494253</v>
+        <v>0.7637795275590551</v>
       </c>
     </row>
     <row r="67">
@@ -6727,27 +6855,27 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Reloncaví</t>
+          <t>Servicio de Salud Chiloé</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Calbuco</t>
+          <t>Castro</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Calbuco</t>
+          <t>Hospital de Castro</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>2</v>
+        <v>335</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>3</v>
+        <v>381</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.8792650918635171</v>
       </c>
     </row>
     <row r="68">
@@ -6758,26 +6886,28 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Reloncaví</t>
+          <t>Servicio de Salud Chiloé</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Frutillar</t>
+          <t>Quellón</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Frutillar</t>
+          <t>Hospital de Quellón</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" s="4" t="n"/>
+        <v>108</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>0.8333333333333334</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -6792,22 +6922,22 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Calbuco</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Puerto Montt</t>
+          <t>Hospital de Calbuco</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>1147</v>
+        <v>2</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>1192</v>
+        <v>3</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>0.962248322147651</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="70">
@@ -6818,120 +6948,116 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Osorno</t>
+          <t>Servicio de Salud Del Reloncaví</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Osorno</t>
+          <t>Frutillar</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Hospital Base San José de Osorno</t>
+          <t>Hospital de Frutillar</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>516</v>
+        <v>1</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>592</v>
-      </c>
-      <c r="G70" s="4" t="n">
-        <v>0.8716216216216216</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Los Rios</t>
+          <t>Servicio de Salud Del Reloncaví</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>La Unión</t>
+          <t>Futaleufú</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Hospital Juan Morey (La Unión)</t>
+          <t>Hospital de Futaleufú</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="G71" s="4" t="n">
-        <v>0.7777777777777778</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Los Rios</t>
+          <t>Servicio de Salud Del Reloncaví</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Lanco</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Lanco</t>
+          <t>Hospital de Puerto Montt</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>1</v>
+        <v>1284</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>1</v>
+        <v>1439</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>1</v>
+        <v>0.8922863099374566</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Los Rios</t>
+          <t>Servicio de Salud Osorno</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Los Lagos</t>
+          <t>Hospital Base San José de Osorno</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>6</v>
+        <v>608</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>6</v>
+        <v>692</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>1</v>
+        <v>0.8786127167630058</v>
       </c>
     </row>
     <row r="74">
@@ -6947,22 +7073,22 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Mariquina</t>
+          <t>La Unión</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Hospital Santa Elisa de San José de la Mariquina</t>
+          <t>Hospital Juan Morey (La Unión)</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>0.9</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="75">
@@ -6978,22 +7104,22 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Paillaco</t>
+          <t>Lanco</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Paillaco</t>
+          <t>Hospital de Lanco</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -7009,22 +7135,22 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Panguipulli</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Panguipulli</t>
+          <t>Hospital de Los Lagos</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>0.625</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -7040,22 +7166,22 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Río Bueno</t>
+          <t>Mariquina</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Río Bueno</t>
+          <t>Hospital Santa Elisa de San José de la Mariquina</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>0.6</v>
+        <v>0.9230769230769231</v>
       </c>
     </row>
     <row r="78">
@@ -7071,177 +7197,177 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Valdivia</t>
+          <t>Paillaco</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Hospital Base Valdivia</t>
+          <t>Hospital de Paillaco</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>516</v>
+        <v>13</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>697</v>
+        <v>16</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>0.7403156384505022</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Magallanes y de la Antártica Chilena</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Magallanes</t>
+          <t>Servicio de Salud Los Rios</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Natales</t>
+          <t>Panguipulli</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Augusto Essmann Burgos ( Natales)</t>
+          <t>Hospital de Panguipulli</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>0.958904109589041</v>
+        <v>0.6111111111111112</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Magallanes y de la Antártica Chilena</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Magallanes</t>
+          <t>Servicio de Salud Los Rios</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Punta Arenas</t>
+          <t>Río Bueno</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Hospital Clínico de Magallanes Dr. Lautaro Navarro Avaria</t>
+          <t>Hospital de Río Bueno</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>305</v>
+        <v>4</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>306</v>
+        <v>6</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>0.9967320261437909</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Los Rios</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
+          <t>Valdivia</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios (Cauquenes)</t>
+          <t>Hospital Base Valdivia</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>37</v>
+        <v>628</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>42</v>
+        <v>834</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>0.8809523809523809</v>
+        <v>0.7529976019184652</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Magallanes y de la Antártica Chilena</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Magallanes</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Constitución</t>
+          <t>Natales</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Constitución</t>
+          <t>Hospital Dr. Augusto Essmann Burgos ( Natales)</t>
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>0.75</v>
+        <v>0.9666666666666667</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Magallanes y de la Antártica Chilena</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Del Maule</t>
+          <t>Servicio de Salud Magallanes</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Curicó</t>
+          <t>Punta Arenas</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios (Curicó)</t>
+          <t>Hospital Clínico de Magallanes Dr. Lautaro Navarro Avaria</t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>847</v>
+        <v>382</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>877</v>
+        <v>376</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>0.9657924743443558</v>
+        <v>1.015957446808511</v>
       </c>
     </row>
     <row r="84">
@@ -7257,22 +7383,22 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Licantén</t>
+          <t>Cauquenes</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Licantén</t>
+          <t>Hospital San Juan de Dios (Cauquenes)</t>
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>0</v>
+        <v>0.8867924528301887</v>
       </c>
     </row>
     <row r="85">
@@ -7288,22 +7414,22 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Linares</t>
+          <t>Constitución</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Hospital Presidente Carlos Ibáñez del Campo (Linares)</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>476</v>
+        <v>19</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>588</v>
+        <v>24</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.7916666666666666</v>
       </c>
     </row>
     <row r="86">
@@ -7319,22 +7445,22 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Parral</t>
+          <t>Curepto</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Hospital San José (Parral)</t>
+          <t>Hospital de Curepto</t>
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>0.5319148936170213</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="87">
@@ -7350,22 +7476,22 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>San Javier</t>
+          <t>Curicó</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Abel Fuentealba Lagos de San Javier</t>
+          <t>Hospital San Juan de Dios (Curicó)</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>18</v>
+        <v>1012</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>32</v>
+        <v>1048</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>0.5625</v>
+        <v>0.9656488549618321</v>
       </c>
     </row>
     <row r="88">
@@ -7381,146 +7507,146 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>Licantén</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. César Garavagno Burotto (Talca)</t>
+          <t>Hospital de Licantén</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>1492</v>
+        <v>0</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>1642</v>
+        <v>1</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>0.9086479902557856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Central</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Maipú</t>
+          <t>Linares</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Hospital Clínico Metropolitano El Carmen Doctor Luis Valentín Ferrada</t>
+          <t>Hospital Presidente Carlos Ibáñez del Campo (Linares)</t>
         </is>
       </c>
       <c r="E89" s="3" t="n">
-        <v>925</v>
+        <v>558</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>955</v>
+        <v>693</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>0.9685863874345549</v>
+        <v>0.8051948051948052</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Central</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Parral</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Hospital Clínico San Borja Arriarán</t>
+          <t>Hospital San José (Parral)</t>
         </is>
       </c>
       <c r="E90" s="3" t="n">
-        <v>1108</v>
+        <v>27</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>1240</v>
+        <v>57</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>0.8935483870967742</v>
+        <v>0.4736842105263158</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Norte</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Colina</t>
+          <t>San Javier</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>SAR Colina</t>
+          <t>Hospital Dr. Abel Fuentealba Lagos de San Javier</t>
         </is>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>0</v>
+        <v>0.4883720930232558</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Metropolitana de Santiago</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Norte</t>
+          <t>Servicio de Salud Del Maule</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Independencia</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Complejo Hospitalario San José (Santiago, Independencia)</t>
+          <t>Hospital Dr. César Garavagno Burotto (Talca)</t>
         </is>
       </c>
       <c r="E92" s="3" t="n">
-        <v>1650</v>
+        <v>1763</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>1881</v>
+        <v>1938</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>0.8771929824561403</v>
+        <v>0.9097007223942208</v>
       </c>
     </row>
     <row r="93">
@@ -7531,27 +7657,27 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Occidente</t>
+          <t>Servicio de Salud Metropolitano Central</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Cerro Navia</t>
+          <t>Maipú</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Hospital  Félix Bulnes Cerda</t>
+          <t>Hospital Clínico Metropolitano El Carmen Doctor Luis Valentín Ferrada</t>
         </is>
       </c>
       <c r="E93" s="3" t="n">
-        <v>951</v>
+        <v>1022</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>1090</v>
+        <v>1140</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>0.8724770642201835</v>
+        <v>0.8964912280701754</v>
       </c>
     </row>
     <row r="94">
@@ -7562,27 +7688,27 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Occidente</t>
+          <t>Servicio de Salud Metropolitano Central</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Melipilla</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Hospital San José (Melipilla)</t>
+          <t>Hospital Clínico San Borja Arriarán</t>
         </is>
       </c>
       <c r="E94" s="3" t="n">
-        <v>472</v>
+        <v>1328</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>571</v>
+        <v>1481</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>0.8266199649737302</v>
+        <v>0.8966914247130318</v>
       </c>
     </row>
     <row r="95">
@@ -7593,27 +7719,27 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Occidente</t>
+          <t>Servicio de Salud Metropolitano Norte</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Peñaflor</t>
+          <t>Colina</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SAR Colina</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>0.7083333333333334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -7624,27 +7750,27 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Occidente</t>
+          <t>Servicio de Salud Metropolitano Norte</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios (Santiago, Santiago)</t>
+          <t>Complejo Hospitalario San José (Santiago, Independencia)</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>910</v>
+        <v>1940</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>931</v>
+        <v>2228</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>0.9774436090225563</v>
+        <v>0.8707360861759426</v>
       </c>
     </row>
     <row r="97">
@@ -7660,22 +7786,22 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Talagante</t>
+          <t>Cerro Navia</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Hospital Adalberto Steeger (Talagante)</t>
+          <t>Hospital  Félix Bulnes Cerda</t>
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>155</v>
+        <v>1164</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>402</v>
+        <v>1308</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>0.3855721393034826</v>
+        <v>0.8899082568807339</v>
       </c>
     </row>
     <row r="98">
@@ -7686,27 +7812,27 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Oriente</t>
+          <t>Servicio de Salud Metropolitano Occidente</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Peñalolén</t>
+          <t>Melipilla</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Luis Tisné B. (Santiago, Peñalolén)</t>
+          <t>Hospital San José (Melipilla)</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>1136</v>
+        <v>581</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>1224</v>
+        <v>684</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>0.9281045751633987</v>
+        <v>0.8494152046783626</v>
       </c>
     </row>
     <row r="99">
@@ -7717,27 +7843,27 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur</t>
+          <t>Servicio de Salud Metropolitano Occidente</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Buin</t>
+          <t>Peñaflor</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Luis (Buin)</t>
+          <t>Hospital de Peñaflor</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>281</v>
+        <v>23</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>306</v>
+        <v>32</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>0.9183006535947712</v>
+        <v>0.71875</v>
       </c>
     </row>
     <row r="100">
@@ -7748,27 +7874,27 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur</t>
+          <t>Servicio de Salud Metropolitano Occidente</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Hospital El Pino (Santiago, San Bernardo)</t>
+          <t>Hospital San Juan de Dios (Santiago, Santiago)</t>
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>779</v>
+        <v>1062</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>812</v>
+        <v>1094</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>0.9593596059113301</v>
+        <v>0.9707495429616088</v>
       </c>
     </row>
     <row r="101">
@@ -7779,27 +7905,27 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur</t>
+          <t>Servicio de Salud Metropolitano Occidente</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>San Bernardo</t>
+          <t>Talagante</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Hospital Parroquial de San Bernardo (D)</t>
+          <t>Hospital Adalberto Steeger (Talagante)</t>
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>447</v>
+        <v>155</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>477</v>
+        <v>402</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>0.9371069182389937</v>
+        <v>0.3855721393034826</v>
       </c>
     </row>
     <row r="102">
@@ -7810,27 +7936,27 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur</t>
+          <t>Servicio de Salud Metropolitano Oriente</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Peñalolén</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Hospital Barros Luco Trudeau (Santiago, San Miguel)</t>
+          <t>Hospital Dr. Luis Tisné B. (Santiago, Peñalolén)</t>
         </is>
       </c>
       <c r="E102" s="3" t="n">
-        <v>813</v>
+        <v>1357</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>1019</v>
+        <v>1461</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>0.7978410206084396</v>
+        <v>0.9288158795345653</v>
       </c>
     </row>
     <row r="103">
@@ -7841,27 +7967,27 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>La Florida</t>
+          <t>Buin</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Hospital Clínico Metropolitano La Florida Dra. Eloísa Díaz Insunza</t>
+          <t>Hospital San Luis (Buin)</t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>750</v>
+        <v>338</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>898</v>
+        <v>366</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>0.8351893095768375</v>
+        <v>0.9234972677595629</v>
       </c>
     </row>
     <row r="104">
@@ -7872,27 +7998,27 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Complejo Hospitalario Dr. Sótero del Río (Santiago, Puente Alto)</t>
+          <t>Hospital El Pino (Santiago, San Bernardo)</t>
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>1025</v>
+        <v>937</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>1264</v>
+        <v>976</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>0.8109177215189873</v>
+        <v>0.9600409836065574</v>
       </c>
     </row>
     <row r="105">
@@ -7903,244 +8029,242 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Sur Oriente</t>
+          <t>Servicio de Salud Metropolitano Sur</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>San Ramón</t>
+          <t>San Bernardo</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado (San Ramón)</t>
+          <t>Hospital Parroquial de San Bernardo (D)</t>
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>754</v>
+        <v>531</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>817</v>
+        <v>569</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>0.9228886168910648</v>
+        <v>0.9332161687170475</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Tarapacá</t>
+          <t>Servicio de Salud Metropolitano Sur</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Alto Hospicio</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Alto Hospicio</t>
+          <t>Hospital Barros Luco Trudeau (Santiago, San Miguel)</t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>18</v>
+        <v>983</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>19</v>
+        <v>1213</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.8103874690849134</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Tarapacá</t>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Iquique</t>
+          <t>La Florida</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Ernesto Torres Galdames (Iquique)</t>
+          <t>Hospital Clínico Metropolitano La Florida Dra. Eloísa Díaz Insunza</t>
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>890</v>
+        <v>902</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>1316</v>
+        <v>1061</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>0.6762917933130699</v>
+        <v>0.8501413760603205</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Aconcagua</t>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Llaillay</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Francisco (Llaillay)</t>
+          <t>Complejo Hospitalario Dr. Sótero del Río (Santiago, Puente Alto)</t>
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>0</v>
+        <v>1185</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>2</v>
+        <v>1494</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>0</v>
+        <v>0.7931726907630522</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Aconcagua</t>
+          <t>Servicio de Salud Metropolitano Sur Oriente</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Ramón</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Juan de Dios (Los Andes)</t>
+          <t>Hospital Padre Alberto Hurtado (San Ramón)</t>
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>265</v>
+        <v>878</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>276</v>
+        <v>956</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>0.9601449275362319</v>
+        <v>0.9184100418410042</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Aconcagua</t>
+          <t>Servicio de Salud Tarapacá</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>San Felipe</t>
+          <t>Alto Hospicio</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Camilo de San Felipe</t>
+          <t>Centro de Salud Familiar Pedro Pulgar Melgarejo</t>
         </is>
       </c>
       <c r="E110" s="3" t="n">
-        <v>491</v>
+        <v>1</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>523</v>
-      </c>
-      <c r="G110" s="4" t="n">
-        <v>0.9388145315487572</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Metropolitano Oriente</t>
+          <t>Servicio de Salud Tarapacá</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Isla de Pascua</t>
+          <t>Alto Hospicio</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Hospital Hanga Roa (Isla De Pascua)</t>
+          <t>Hospital de Alto Hospicio</t>
         </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>1.114285714285714</v>
+        <v>0.967741935483871</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Valparaíso San Antonio</t>
+          <t>Servicio de Salud Tarapacá</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Iquique</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Hospital Claudio Vicuña (San Antonio)</t>
+          <t>Hospital Dr. Ernesto Torres Galdames (Iquique)</t>
         </is>
       </c>
       <c r="E112" s="3" t="n">
-        <v>458</v>
+        <v>1054</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>483</v>
+        <v>1588</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>0.94824016563147</v>
+        <v>0.663727959697733</v>
       </c>
     </row>
     <row r="113">
@@ -8151,27 +8275,27 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Valparaíso San Antonio</t>
+          <t>Servicio de Salud Aconcagua</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Llaillay</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Hospital Carlos Van Buren (Valparaíso)</t>
+          <t>Hospital San Francisco (Llaillay)</t>
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>574</v>
+        <v>0</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>633</v>
+        <v>2</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>0.9067930489731437</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -8182,27 +8306,27 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
+          <t>Servicio de Salud Aconcagua</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Cabildo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Víctor Hugo Moll (Cabildo)</t>
+          <t>Hospital San Juan de Dios (Los Andes)</t>
         </is>
       </c>
       <c r="E114" s="3" t="n">
-        <v>1</v>
+        <v>331</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>2</v>
+        <v>344</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>0.5</v>
+        <v>0.9622093023255814</v>
       </c>
     </row>
     <row r="115">
@@ -8213,27 +8337,27 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
+          <t>Servicio de Salud Aconcagua</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Calera</t>
+          <t>San Felipe</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Mario Sánchez Vergara (La Calera)</t>
+          <t>Hospital San Camilo de San Felipe</t>
         </is>
       </c>
       <c r="E115" s="3" t="n">
-        <v>1</v>
+        <v>580</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>2</v>
+        <v>620</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>0.5</v>
+        <v>0.9354838709677419</v>
       </c>
     </row>
     <row r="116">
@@ -8244,27 +8368,27 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
+          <t>Servicio de Salud Metropolitano Oriente</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>La Ligua</t>
+          <t>Isla de Pascua</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Hospital San Agustín (La Ligua)</t>
+          <t>Hospital Hanga Roa (Isla De Pascua)</t>
         </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>0.25</v>
+        <v>1.093023255813953</v>
       </c>
     </row>
     <row r="117">
@@ -8275,27 +8399,27 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
+          <t>Servicio de Salud Valparaíso San Antonio</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Limache</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Hospital Santo Tomás (Limache)</t>
+          <t>Hospital Claudio Vicuña (San Antonio)</t>
         </is>
       </c>
       <c r="E117" s="3" t="n">
-        <v>1</v>
+        <v>550</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>2</v>
+        <v>579</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>0.5</v>
+        <v>0.9499136442141624</v>
       </c>
     </row>
     <row r="118">
@@ -8306,27 +8430,27 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Viña del Mar Quillota</t>
+          <t>Servicio de Salud Valparaíso San Antonio</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Quillota</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Hospital Biprovincial Quillota Petorca</t>
+          <t>Hospital Carlos Van Buren (Valparaíso)</t>
         </is>
       </c>
       <c r="E118" s="3" t="n">
-        <v>521</v>
+        <v>698</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>579</v>
+        <v>764</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>0.8998272884283247</v>
+        <v>0.9136125654450262</v>
       </c>
     </row>
     <row r="119">
@@ -8342,22 +8466,22 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Quilpué</t>
+          <t>Cabildo</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Hospital de Quilpué</t>
+          <t>Hospital Dr. Víctor Hugo Moll (Cabildo)</t>
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>196</v>
+        <v>2</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>417</v>
+        <v>3</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>0.4700239808153477</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="120">
@@ -8373,150 +8497,336 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Viña del Mar</t>
+          <t>Calera</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Hospital Dr. Gustavo Fricke (Viña del Mar)</t>
+          <t>Hospital Dr. Mario Sánchez Vergara (La Calera)</t>
         </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v>779</v>
+        <v>2</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>850</v>
+        <v>4</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>0.9164705882352941</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Ñuble</t>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Bulnes</t>
+          <t>La Ligua</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
+          <t>Hospital San Agustín (La Ligua)</t>
         </is>
       </c>
       <c r="E121" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Ñuble</t>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Chillán</t>
+          <t>Limache</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Hospital Clínico Herminda Martín (Chillán)</t>
+          <t>Hospital Santo Tomás (Limache)</t>
         </is>
       </c>
       <c r="E122" s="3" t="n">
-        <v>643</v>
+        <v>2</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>754</v>
+        <v>3</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>0.8527851458885941</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Servicio de Salud Ñuble</t>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Quirihue</t>
+          <t>Quillota</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Salud Familiar de Quirihue</t>
+          <t>Hospital Biprovincial Quillota Petorca</t>
         </is>
       </c>
       <c r="E123" s="3" t="n">
-        <v>6</v>
+        <v>606</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>6</v>
+        <v>676</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>1</v>
+        <v>0.8964497041420119</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Quilpué</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Hospital de Quilpué</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>237</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>502</v>
+      </c>
+      <c r="G124" s="4" t="n">
+        <v>0.4721115537848606</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Quintero</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Adriana Cousiño (Quintero)</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Viña del Mar Quillota</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Viña del Mar</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Dr. Gustavo Fricke (Viña del Mar)</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>922</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>1030</v>
+      </c>
+      <c r="G126" s="4" t="n">
+        <v>0.8951456310679612</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
           <t>Ñuble</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>Servicio de Salud Ñuble</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Bulnes</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F127" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G127" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Clínico Herminda Martín (Chillán)</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>782</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>904</v>
+      </c>
+      <c r="G128" s="4" t="n">
+        <v>0.8650442477876106</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Quirihue</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Hospital Comunitario de Salud Familiar de Quirihue</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="G129" s="4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Servicio de Salud Ñuble</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
         <is>
           <t>San Carlos</t>
         </is>
       </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Hospital de San Carlos</t>
         </is>
       </c>
-      <c r="E124" s="3" t="n">
-        <v>187</v>
-      </c>
-      <c r="F124" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="G124" s="4" t="n">
-        <v>0.9842105263157894</v>
+      <c r="E130" s="3" t="n">
+        <v>217</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>220</v>
+      </c>
+      <c r="G130" s="4" t="n">
+        <v>0.9863636363636363</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G124"/>
+  <autoFilter ref="A1:G130"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>